--- a/tams-invest-parent/tams-invest-period/src/main/resources/tpl/TrdDepoDuration001.xlsx
+++ b/tams-invest-parent/tams-invest-period/src/main/resources/tpl/TrdDepoDuration001.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workspace\2.1.0new\2.1.0\tams-invest-parent\tams-invest-period\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\ChongQingTouZi\tams\tams-invest-parent\tams-invest-period\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20390" windowHeight="8520"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20388" windowHeight="8520"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>有效状态</t>
   </si>
@@ -59,10 +59,6 @@
   </si>
   <si>
     <t>资金到账日</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>通道</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -421,55 +417,52 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.90625" customWidth="1"/>
-    <col min="2" max="3" width="21" customWidth="1"/>
-    <col min="4" max="7" width="16.7265625" customWidth="1"/>
-    <col min="8" max="8" width="17.36328125" customWidth="1"/>
-    <col min="9" max="10" width="14.08984375" customWidth="1"/>
-    <col min="11" max="13" width="10.90625" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="6" width="16.77734375" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" customWidth="1"/>
+    <col min="8" max="9" width="14.109375" customWidth="1"/>
+    <col min="10" max="12" width="10.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
+      <c r="C1" t="s">
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
       <c r="H1" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
       <c r="K1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L1" t="s">
-        <v>5</v>
-      </c>
-      <c r="M1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/tams-invest-parent/tams-invest-period/src/main/resources/tpl/TrdDepoDuration001.xlsx
+++ b/tams-invest-parent/tams-invest-period/src/main/resources/tpl/TrdDepoDuration001.xlsx
@@ -1,15 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\ChongQingTouZi\tams\tams-invest-parent\tams-invest-period\src\main\resources\tpl\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20388" windowHeight="8520"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20385" windowHeight="8520"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>有效状态</t>
   </si>
@@ -58,7 +53,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>资金到账日</t>
+    <t>实际结息日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>理论支付日</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -417,18 +416,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="8.875" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="6" width="16.77734375" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" customWidth="1"/>
-    <col min="8" max="9" width="14.109375" customWidth="1"/>
-    <col min="10" max="12" width="10.88671875" customWidth="1"/>
+    <col min="3" max="6" width="16.75" customWidth="1"/>
+    <col min="7" max="7" width="17.375" customWidth="1"/>
+    <col min="8" max="9" width="14.125" customWidth="1"/>
+    <col min="10" max="12" width="10.875" customWidth="1"/>
+    <col min="13" max="13" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -464,6 +464,9 @@
       </c>
       <c r="L1" t="s">
         <v>6</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
